--- a/Result/profitability/2392.xlsx
+++ b/Result/profitability/2392.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.47</v>
+        <v>0.9712499999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>3.945</v>
+        <v>2.5125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5675</v>
+        <v>0.9662499999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>3.59</v>
+        <v>2.7075</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3825</v>
+        <v>1.21125</v>
       </c>
       <c r="N4" t="n">
-        <v>3.97375</v>
+        <v>2.61875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3675</v>
+        <v>1.5225</v>
       </c>
       <c r="N5" t="n">
-        <v>3.34375</v>
+        <v>6.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03749999999999999</v>
+        <v>1.96375</v>
       </c>
       <c r="N6" t="n">
-        <v>7.06</v>
+        <v>10.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4</v>
+        <v>2.25375</v>
       </c>
       <c r="N7" t="n">
-        <v>11.47125</v>
+        <v>12.20375</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.75125</v>
+        <v>2.43625</v>
       </c>
       <c r="N8" t="n">
-        <v>13.31</v>
+        <v>11.42375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1518,7 +1518,7 @@
         <v>1.05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9400000000000002</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>12.955</v>
@@ -1772,7 +1772,7 @@
         <v>0.48</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7875</v>
+        <v>0.7875000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>12.57875</v>
@@ -1899,7 +1899,7 @@
         <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7812500000000001</v>
+        <v>0.78125</v>
       </c>
       <c r="N12" t="n">
         <v>12.5275</v>
@@ -2026,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8575000000000002</v>
+        <v>0.8575</v>
       </c>
       <c r="N13" t="n">
         <v>12.80875</v>
@@ -9344,15 +9344,15 @@
         <v>-17.66</v>
       </c>
       <c r="G71" t="n">
-        <v>-6019</v>
+        <v>-6040</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-28.17%</t>
+          <t>-28.26%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-769</v>
+        <v>-748</v>
       </c>
       <c r="J71" t="n">
         <v>-6789</v>
@@ -9471,15 +9471,15 @@
         <v>-23.13</v>
       </c>
       <c r="G72" t="n">
-        <v>-8573</v>
+        <v>-8553</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-32.40%</t>
+          <t>-32.32%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="J72" t="n">
         <v>-8180</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2392</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17641</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16895</v>
+      </c>
+      <c r="E75" t="n">
+        <v>746</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1351</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7867</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6516</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6024</v>
+      </c>
+      <c r="L75" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.02125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2.8975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-29.30434782608695</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-15.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.781055900621118</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.199999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.239524348810872</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
